--- a/backend/data/financials_by_company/13O.F.xlsx
+++ b/backend/data/financials_by_company/13O.F.xlsx
@@ -677,610 +677,610 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-2722.868905</v>
+        <v>1345.420425</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00039</v>
+        <v>0.000251</v>
       </c>
       <c r="D2" t="n">
-        <v>-75526000</v>
+        <v>-107601000</v>
       </c>
       <c r="E2" t="n">
-        <v>-6975000</v>
+        <v>5356000</v>
       </c>
       <c r="F2" t="n">
-        <v>-6975000</v>
+        <v>5356000</v>
       </c>
       <c r="G2" t="n">
-        <v>-89191000</v>
+        <v>-303139000</v>
       </c>
       <c r="H2" t="n">
-        <v>1638000</v>
+        <v>26665000</v>
       </c>
       <c r="I2" t="n">
-        <v>45872000</v>
+        <v>87670000</v>
       </c>
       <c r="J2" t="n">
-        <v>-82501000</v>
+        <v>-102245000</v>
       </c>
       <c r="K2" t="n">
-        <v>-84139000</v>
+        <v>-128910000</v>
       </c>
       <c r="L2" t="n">
-        <v>344000</v>
+        <v>-4384000</v>
       </c>
       <c r="M2" t="n">
-        <v>395000</v>
+        <v>6441000</v>
       </c>
       <c r="N2" t="n">
-        <v>739000</v>
+        <v>2057000</v>
       </c>
       <c r="O2" t="n">
-        <v>-82218722.86890499</v>
+        <v>-308493654.579575</v>
       </c>
       <c r="P2" t="n">
-        <v>-89191000</v>
+        <v>26504000</v>
       </c>
       <c r="Q2" t="n">
-        <v>115842000</v>
+        <v>281354000</v>
       </c>
       <c r="R2" t="n">
-        <v>1072199000</v>
+        <v>1055122400</v>
       </c>
       <c r="S2" t="n">
-        <v>1072199000</v>
+        <v>1055122400</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0832</v>
+        <v>0.0251</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0832</v>
+        <v>0.0251</v>
       </c>
       <c r="V2" t="n">
-        <v>-89191000</v>
+        <v>26504000</v>
       </c>
       <c r="W2" t="n">
-        <v>-89191000</v>
+        <v>26504000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-89191000</v>
+        <v>26504000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-4690000</v>
+        <v>-167822000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-84501000</v>
+        <v>194326000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>329643000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-84501000</v>
+        <v>-135317000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-33000</v>
+        <v>-34000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-84534000</v>
+        <v>-135351000</v>
       </c>
       <c r="AF2" t="n">
-        <v>60000</v>
+        <v>989000</v>
       </c>
       <c r="AG2" t="n">
-        <v>3015000</v>
+        <v>19464000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-535000</v>
+        <v>-19949000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2480000</v>
+        <v>485000</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>344000</v>
+        <v>-4384000</v>
       </c>
       <c r="AM2" t="n">
-        <v>395000</v>
+        <v>6441000</v>
       </c>
       <c r="AN2" t="n">
-        <v>739000</v>
+        <v>2057000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-23654000</v>
+        <v>-137539000</v>
       </c>
       <c r="AP2" t="n">
-        <v>69970000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-3775000</v>
-      </c>
+        <v>193684000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>16132000</v>
+        <v>24141000</v>
       </c>
       <c r="AS2" t="n">
-        <v>57492000</v>
+        <v>150857000</v>
       </c>
       <c r="AT2" t="n">
-        <v>16141000</v>
+        <v>21981000</v>
       </c>
       <c r="AU2" t="n">
-        <v>41351000</v>
+        <v>128876000</v>
       </c>
       <c r="AV2" t="n">
-        <v>46316000</v>
+        <v>56145000</v>
       </c>
       <c r="AW2" t="n">
-        <v>45872000</v>
+        <v>87670000</v>
       </c>
       <c r="AX2" t="n">
-        <v>92188000</v>
+        <v>143815000</v>
       </c>
       <c r="AY2" t="n">
-        <v>92188000</v>
+        <v>143815000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-10677000</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-27225000</v>
+        <v>-52917000</v>
       </c>
       <c r="E3" t="n">
-        <v>-42708000</v>
+        <v>2620000</v>
       </c>
       <c r="F3" t="n">
-        <v>-42708000</v>
+        <v>2620000</v>
       </c>
       <c r="G3" t="n">
-        <v>-78590000</v>
+        <v>-29609000</v>
       </c>
       <c r="H3" t="n">
-        <v>5999000</v>
+        <v>22368000</v>
       </c>
       <c r="I3" t="n">
-        <v>44111000</v>
+        <v>133797000</v>
       </c>
       <c r="J3" t="n">
-        <v>-69933000</v>
+        <v>-50297000</v>
       </c>
       <c r="K3" t="n">
-        <v>-75932000</v>
+        <v>-72665000</v>
       </c>
       <c r="L3" t="n">
-        <v>198000</v>
+        <v>729000</v>
       </c>
       <c r="M3" t="n">
-        <v>335000</v>
+        <v>4749000</v>
       </c>
       <c r="N3" t="n">
-        <v>533000</v>
+        <v>5478000</v>
       </c>
       <c r="O3" t="n">
-        <v>-46559000</v>
+        <v>-32229000</v>
       </c>
       <c r="P3" t="n">
-        <v>-62765000</v>
+        <v>-29609000</v>
       </c>
       <c r="Q3" t="n">
-        <v>116198000</v>
+        <v>307803000</v>
       </c>
       <c r="R3" t="n">
-        <v>1063168000</v>
+        <v>1073222248</v>
       </c>
       <c r="S3" t="n">
-        <v>1063168000</v>
+        <v>1073222248</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.059</v>
+        <v>-0.0276</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.059</v>
+        <v>-0.0276</v>
       </c>
       <c r="V3" t="n">
-        <v>-62765000</v>
+        <v>-29609000</v>
       </c>
       <c r="W3" t="n">
-        <v>-62765000</v>
+        <v>-29609000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-62765000</v>
+        <v>-29609000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-2281000</v>
+        <v>47805000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-60484000</v>
+        <v>-77414000</v>
       </c>
       <c r="AB3" t="n">
-        <v>15825000</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-76309000</v>
+        <v>-77414000</v>
       </c>
       <c r="AD3" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-76267000</v>
+        <v>-77414000</v>
       </c>
       <c r="AF3" t="n">
-        <v>33000</v>
+        <v>9509000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-11266000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-3806000</v>
-      </c>
+        <v>3949000</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>10561000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>8273000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-3762000</v>
-      </c>
+        <v>-3949000</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>198000</v>
+        <v>729000</v>
       </c>
       <c r="AM3" t="n">
-        <v>335000</v>
+        <v>4749000</v>
       </c>
       <c r="AN3" t="n">
-        <v>533000</v>
+        <v>5478000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-27202000</v>
+        <v>-90091000</v>
       </c>
       <c r="AP3" t="n">
-        <v>72087000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-3011000</v>
-      </c>
+        <v>174006000</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>15753000</v>
+        <v>18778000</v>
       </c>
       <c r="AS3" t="n">
-        <v>57941000</v>
+        <v>143245000</v>
       </c>
       <c r="AT3" t="n">
-        <v>13978000</v>
+        <v>21520000</v>
       </c>
       <c r="AU3" t="n">
-        <v>43963000</v>
+        <v>121725000</v>
       </c>
       <c r="AV3" t="n">
-        <v>44885000</v>
+        <v>83915000</v>
       </c>
       <c r="AW3" t="n">
-        <v>44111000</v>
+        <v>133797000</v>
       </c>
       <c r="AX3" t="n">
-        <v>88996000</v>
+        <v>217712000</v>
       </c>
       <c r="AY3" t="n">
-        <v>88996000</v>
+        <v>217712000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-10677000</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-52917000</v>
+        <v>-27225000</v>
       </c>
       <c r="E4" t="n">
-        <v>2620000</v>
+        <v>-42708000</v>
       </c>
       <c r="F4" t="n">
-        <v>2620000</v>
+        <v>-42708000</v>
       </c>
       <c r="G4" t="n">
-        <v>-29609000</v>
+        <v>-78590000</v>
       </c>
       <c r="H4" t="n">
-        <v>22368000</v>
+        <v>5999000</v>
       </c>
       <c r="I4" t="n">
-        <v>133797000</v>
+        <v>44111000</v>
       </c>
       <c r="J4" t="n">
-        <v>-50297000</v>
+        <v>-69933000</v>
       </c>
       <c r="K4" t="n">
-        <v>-72665000</v>
+        <v>-75932000</v>
       </c>
       <c r="L4" t="n">
-        <v>729000</v>
+        <v>198000</v>
       </c>
       <c r="M4" t="n">
-        <v>4749000</v>
+        <v>335000</v>
       </c>
       <c r="N4" t="n">
-        <v>5478000</v>
+        <v>533000</v>
       </c>
       <c r="O4" t="n">
-        <v>-32229000</v>
+        <v>-46559000</v>
       </c>
       <c r="P4" t="n">
-        <v>-29609000</v>
+        <v>-62765000</v>
       </c>
       <c r="Q4" t="n">
-        <v>307803000</v>
+        <v>116198000</v>
       </c>
       <c r="R4" t="n">
-        <v>1073222248</v>
+        <v>1063168000</v>
       </c>
       <c r="S4" t="n">
-        <v>1073222248</v>
+        <v>1063168000</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0276</v>
+        <v>-0.059</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0276</v>
+        <v>-0.059</v>
       </c>
       <c r="V4" t="n">
-        <v>-29609000</v>
+        <v>-62765000</v>
       </c>
       <c r="W4" t="n">
-        <v>-29609000</v>
+        <v>-62765000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-29609000</v>
+        <v>-62765000</v>
       </c>
       <c r="Z4" t="n">
-        <v>47805000</v>
+        <v>-2281000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-77414000</v>
+        <v>-60484000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>15825000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-77414000</v>
+        <v>-76309000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-77414000</v>
+        <v>-76267000</v>
       </c>
       <c r="AF4" t="n">
-        <v>9509000</v>
+        <v>33000</v>
       </c>
       <c r="AG4" t="n">
-        <v>3949000</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>-11266000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-3806000</v>
+      </c>
       <c r="AI4" t="n">
-        <v>-3949000</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+        <v>10561000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>8273000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-3762000</v>
+      </c>
       <c r="AL4" t="n">
-        <v>729000</v>
+        <v>198000</v>
       </c>
       <c r="AM4" t="n">
-        <v>4749000</v>
+        <v>335000</v>
       </c>
       <c r="AN4" t="n">
-        <v>5478000</v>
+        <v>533000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-90091000</v>
+        <v>-27202000</v>
       </c>
       <c r="AP4" t="n">
-        <v>174006000</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
+        <v>72087000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-3011000</v>
+      </c>
       <c r="AR4" t="n">
-        <v>18778000</v>
+        <v>15753000</v>
       </c>
       <c r="AS4" t="n">
-        <v>143245000</v>
+        <v>57941000</v>
       </c>
       <c r="AT4" t="n">
-        <v>21520000</v>
+        <v>13978000</v>
       </c>
       <c r="AU4" t="n">
-        <v>121725000</v>
+        <v>43963000</v>
       </c>
       <c r="AV4" t="n">
-        <v>83915000</v>
+        <v>44885000</v>
       </c>
       <c r="AW4" t="n">
-        <v>133797000</v>
+        <v>44111000</v>
       </c>
       <c r="AX4" t="n">
-        <v>217712000</v>
+        <v>88996000</v>
       </c>
       <c r="AY4" t="n">
-        <v>217712000</v>
+        <v>88996000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1345.420425</v>
+        <v>-2722.868905</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000251</v>
+        <v>0.00039</v>
       </c>
       <c r="D5" t="n">
-        <v>-107601000</v>
+        <v>-75526000</v>
       </c>
       <c r="E5" t="n">
-        <v>5356000</v>
+        <v>-6975000</v>
       </c>
       <c r="F5" t="n">
-        <v>5356000</v>
+        <v>-6975000</v>
       </c>
       <c r="G5" t="n">
-        <v>-303139000</v>
+        <v>-89191000</v>
       </c>
       <c r="H5" t="n">
-        <v>26665000</v>
+        <v>1638000</v>
       </c>
       <c r="I5" t="n">
-        <v>87670000</v>
+        <v>45872000</v>
       </c>
       <c r="J5" t="n">
-        <v>-102245000</v>
+        <v>-82501000</v>
       </c>
       <c r="K5" t="n">
-        <v>-128910000</v>
+        <v>-84139000</v>
       </c>
       <c r="L5" t="n">
-        <v>-4384000</v>
+        <v>344000</v>
       </c>
       <c r="M5" t="n">
-        <v>6441000</v>
+        <v>395000</v>
       </c>
       <c r="N5" t="n">
-        <v>2057000</v>
+        <v>739000</v>
       </c>
       <c r="O5" t="n">
-        <v>-308493654.579575</v>
+        <v>-82218722.86890499</v>
       </c>
       <c r="P5" t="n">
-        <v>26504000</v>
+        <v>-89191000</v>
       </c>
       <c r="Q5" t="n">
-        <v>281354000</v>
+        <v>115842000</v>
       </c>
       <c r="R5" t="n">
-        <v>1055122400</v>
+        <v>1072199000</v>
       </c>
       <c r="S5" t="n">
-        <v>1055122400</v>
+        <v>1072199000</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0251</v>
+        <v>-0.0832</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0251</v>
+        <v>-0.0832</v>
       </c>
       <c r="V5" t="n">
-        <v>26504000</v>
+        <v>-89191000</v>
       </c>
       <c r="W5" t="n">
-        <v>26504000</v>
+        <v>-89191000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>26504000</v>
+        <v>-89191000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-167822000</v>
+        <v>-4690000</v>
       </c>
       <c r="AA5" t="n">
-        <v>194326000</v>
+        <v>-84501000</v>
       </c>
       <c r="AB5" t="n">
-        <v>329643000</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-135317000</v>
+        <v>-84501000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-34000</v>
+        <v>-33000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-135351000</v>
+        <v>-84534000</v>
       </c>
       <c r="AF5" t="n">
-        <v>989000</v>
+        <v>60000</v>
       </c>
       <c r="AG5" t="n">
-        <v>19464000</v>
+        <v>3015000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-19949000</v>
+        <v>-535000</v>
       </c>
       <c r="AI5" t="n">
-        <v>485000</v>
+        <v>-2480000</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
-      <c r="AK5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
       <c r="AL5" t="n">
-        <v>-4384000</v>
+        <v>344000</v>
       </c>
       <c r="AM5" t="n">
-        <v>6441000</v>
+        <v>395000</v>
       </c>
       <c r="AN5" t="n">
-        <v>2057000</v>
+        <v>739000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-137539000</v>
+        <v>-23654000</v>
       </c>
       <c r="AP5" t="n">
-        <v>193684000</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
+        <v>69970000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-3775000</v>
+      </c>
       <c r="AR5" t="n">
-        <v>24141000</v>
+        <v>16132000</v>
       </c>
       <c r="AS5" t="n">
-        <v>150857000</v>
+        <v>57492000</v>
       </c>
       <c r="AT5" t="n">
-        <v>21981000</v>
+        <v>16141000</v>
       </c>
       <c r="AU5" t="n">
-        <v>128876000</v>
+        <v>41351000</v>
       </c>
       <c r="AV5" t="n">
-        <v>56145000</v>
+        <v>46316000</v>
       </c>
       <c r="AW5" t="n">
-        <v>87670000</v>
+        <v>45872000</v>
       </c>
       <c r="AX5" t="n">
-        <v>143815000</v>
+        <v>92188000</v>
       </c>
       <c r="AY5" t="n">
-        <v>143815000</v>
+        <v>92188000</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>1077799887</v>
@@ -1655,47 +1655,41 @@
         <v>1077799887</v>
       </c>
       <c r="D2" t="n">
-        <v>9941000</v>
+        <v>57188000</v>
       </c>
       <c r="E2" t="n">
-        <v>73258000</v>
+        <v>277180000</v>
       </c>
       <c r="F2" t="n">
-        <v>75858000</v>
+        <v>279591000</v>
       </c>
       <c r="G2" t="n">
-        <v>19368000</v>
+        <v>633625000</v>
       </c>
       <c r="H2" t="n">
-        <v>73258000</v>
+        <v>277180000</v>
       </c>
       <c r="I2" t="n">
-        <v>7341000</v>
+        <v>57188000</v>
       </c>
       <c r="J2" t="n">
-        <v>73258000</v>
+        <v>279591000</v>
       </c>
       <c r="K2" t="n">
-        <v>73258000</v>
+        <v>279591000</v>
       </c>
       <c r="L2" t="n">
-        <v>66893000</v>
+        <v>687987000</v>
       </c>
       <c r="M2" t="n">
-        <v>-6365000</v>
+        <v>408396000</v>
       </c>
       <c r="N2" t="n">
-        <v>73258000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>47452000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-1035075000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1023563000</v>
-      </c>
+        <v>279591000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>335000</v>
       </c>
@@ -1703,142 +1697,152 @@
         <v>335000</v>
       </c>
       <c r="T2" t="n">
-        <v>33586000</v>
+        <v>122038000</v>
       </c>
       <c r="U2" t="n">
-        <v>5253000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>17000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2000</v>
-      </c>
+        <v>49731000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>5234000</v>
+        <v>49731000</v>
       </c>
       <c r="Y2" t="n">
-        <v>5234000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>49731000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
       <c r="AA2" t="n">
-        <v>28333000</v>
+        <v>72307000</v>
       </c>
       <c r="AB2" t="n">
-        <v>4707000</v>
+        <v>7457000</v>
       </c>
       <c r="AC2" t="n">
-        <v>2107000</v>
+        <v>7457000</v>
       </c>
       <c r="AD2" t="n">
-        <v>2600000</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>10707000</v>
+        <v>30713000</v>
       </c>
       <c r="AF2" t="n">
-        <v>5047000</v>
+        <v>20472000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1347000</v>
+        <v>188000</v>
       </c>
       <c r="AH2" t="n">
-        <v>4313000</v>
+        <v>10053000</v>
       </c>
       <c r="AI2" t="n">
-        <v>100479000</v>
+        <v>810025000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>52778000</v>
+        <v>104093000</v>
       </c>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>10000</v>
-      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>14215000</v>
+        <v>48615000</v>
       </c>
       <c r="AO2" t="n">
-        <v>14215000</v>
+        <v>48615000</v>
       </c>
       <c r="AP2" t="n">
-        <v>32701000</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>32701000</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>1310000</v>
+        <v>2900000</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+        <v>2411000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2411000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
       <c r="AV2" t="n">
-        <v>4542000</v>
+        <v>50167000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-35557000</v>
+        <v>-139107000</v>
       </c>
       <c r="AX2" t="n">
-        <v>40099000</v>
+        <v>189274000</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>77000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>78665000</v>
+      </c>
       <c r="BA2" t="n">
-        <v>15964000</v>
+        <v>38775000</v>
       </c>
       <c r="BB2" t="n">
-        <v>24135000</v>
+        <v>71757000</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>47701000</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+        <v>705932000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>34897000</v>
+      </c>
       <c r="BG2" t="n">
-        <v>10319000</v>
+        <v>52642000</v>
       </c>
       <c r="BH2" t="n">
-        <v>480000</v>
+        <v>565000</v>
       </c>
       <c r="BI2" t="n">
-        <v>20420000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1245000</v>
-      </c>
+        <v>-5102000</v>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="n">
-        <v>1597000</v>
+        <v>6283000</v>
       </c>
       <c r="BL2" t="n">
-        <v>-785000</v>
+        <v>-943000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2382000</v>
+        <v>7226000</v>
       </c>
       <c r="BN2" t="n">
-        <v>13640000</v>
-      </c>
-      <c r="BO2" t="inlineStr"/>
+        <v>616647000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>7577000</v>
+      </c>
       <c r="BP2" t="n">
-        <v>13640000</v>
-      </c>
-      <c r="BQ2" t="inlineStr"/>
+        <v>609070000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0</v>
+      </c>
       <c r="BR2" t="n">
-        <v>13640000</v>
+        <v>609070000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1077799887</v>
@@ -1847,47 +1851,41 @@
         <v>1077799887</v>
       </c>
       <c r="D3" t="n">
-        <v>5299000</v>
+        <v>59727000</v>
       </c>
       <c r="E3" t="n">
-        <v>161832000</v>
+        <v>281606000</v>
       </c>
       <c r="F3" t="n">
-        <v>161832000</v>
+        <v>284485000</v>
       </c>
       <c r="G3" t="n">
-        <v>40238000</v>
+        <v>621970000</v>
       </c>
       <c r="H3" t="n">
-        <v>161832000</v>
+        <v>281606000</v>
       </c>
       <c r="I3" t="n">
-        <v>5299000</v>
+        <v>58727000</v>
       </c>
       <c r="J3" t="n">
-        <v>161832000</v>
+        <v>283485000</v>
       </c>
       <c r="K3" t="n">
-        <v>161832000</v>
+        <v>283485000</v>
       </c>
       <c r="L3" t="n">
-        <v>150889000</v>
+        <v>666216000</v>
       </c>
       <c r="M3" t="n">
-        <v>-10943000</v>
+        <v>382731000</v>
       </c>
       <c r="N3" t="n">
-        <v>161832000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>107016000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-1005605000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1023563000</v>
-      </c>
+        <v>283485000</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>335000</v>
       </c>
@@ -1895,142 +1893,148 @@
         <v>335000</v>
       </c>
       <c r="T3" t="n">
-        <v>36566000</v>
+        <v>107384000</v>
       </c>
       <c r="U3" t="n">
-        <v>3396000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>17000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2000</v>
-      </c>
+        <v>47599000</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>3377000</v>
+        <v>47599000</v>
       </c>
       <c r="Y3" t="n">
-        <v>3377000</v>
+        <v>47599000</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>33170000</v>
+        <v>59785000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1922000</v>
+        <v>12128000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1922000</v>
+        <v>11128000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>17466000</v>
+        <v>31150000</v>
       </c>
       <c r="AF3" t="n">
-        <v>11395000</v>
+        <v>17471000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1934000</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>4137000</v>
+        <v>13679000</v>
       </c>
       <c r="AI3" t="n">
-        <v>187455000</v>
+        <v>773600000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>114047000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>91845000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>344000</v>
+      </c>
       <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="n">
-        <v>10000</v>
-      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>26469000</v>
+        <v>45846000</v>
       </c>
       <c r="AO3" t="n">
-        <v>26469000</v>
+        <v>45846000</v>
       </c>
       <c r="AP3" t="n">
-        <v>86028000</v>
+        <v>1240000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>86028000</v>
+        <v>1240000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1540000</v>
+        <v>2900000</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
+        <v>1879000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1879000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>344000</v>
+      </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>39636000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-36964000</v>
+        <v>-161764000</v>
       </c>
       <c r="AX3" t="n">
-        <v>36964000</v>
+        <v>39636000</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
+        <v>677000</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>39636000</v>
+      </c>
       <c r="BA3" t="n">
-        <v>17373000</v>
+        <v>39740000</v>
       </c>
       <c r="BB3" t="n">
-        <v>19591000</v>
+        <v>75466000</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>73408000</v>
+        <v>681755000</v>
       </c>
       <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BF3" t="n">
+        <v>34614000</v>
+      </c>
       <c r="BG3" t="n">
-        <v>13179000</v>
+        <v>63068000</v>
       </c>
       <c r="BH3" t="n">
-        <v>478000</v>
+        <v>549000</v>
       </c>
       <c r="BI3" t="n">
-        <v>21956000</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1570000</v>
-      </c>
+        <v>-552000</v>
+      </c>
+      <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>763000</v>
+        <v>12185000</v>
       </c>
       <c r="BL3" t="n">
-        <v>-723000</v>
+        <v>-1089000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1486000</v>
+        <v>13274000</v>
       </c>
       <c r="BN3" t="n">
-        <v>35462000</v>
-      </c>
-      <c r="BO3" t="inlineStr"/>
+        <v>571891000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>484602000</v>
+      </c>
       <c r="BP3" t="n">
-        <v>35462000</v>
-      </c>
-      <c r="BQ3" t="inlineStr"/>
+        <v>87289000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>484602000</v>
+      </c>
       <c r="BR3" t="n">
-        <v>35462000</v>
+        <v>87289000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1077799887</v>
@@ -2039,41 +2043,47 @@
         <v>1077799887</v>
       </c>
       <c r="D4" t="n">
-        <v>59727000</v>
+        <v>5299000</v>
       </c>
       <c r="E4" t="n">
-        <v>281606000</v>
+        <v>161832000</v>
       </c>
       <c r="F4" t="n">
-        <v>284485000</v>
+        <v>161832000</v>
       </c>
       <c r="G4" t="n">
-        <v>621970000</v>
+        <v>40238000</v>
       </c>
       <c r="H4" t="n">
-        <v>281606000</v>
+        <v>161832000</v>
       </c>
       <c r="I4" t="n">
-        <v>58727000</v>
+        <v>5299000</v>
       </c>
       <c r="J4" t="n">
-        <v>283485000</v>
+        <v>161832000</v>
       </c>
       <c r="K4" t="n">
-        <v>283485000</v>
+        <v>161832000</v>
       </c>
       <c r="L4" t="n">
-        <v>666216000</v>
+        <v>150889000</v>
       </c>
       <c r="M4" t="n">
-        <v>382731000</v>
+        <v>-10943000</v>
       </c>
       <c r="N4" t="n">
-        <v>283485000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+        <v>161832000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>107016000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-1005605000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1023563000</v>
+      </c>
       <c r="R4" t="n">
         <v>335000</v>
       </c>
@@ -2081,148 +2091,142 @@
         <v>335000</v>
       </c>
       <c r="T4" t="n">
-        <v>107384000</v>
+        <v>36566000</v>
       </c>
       <c r="U4" t="n">
-        <v>47599000</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>3396000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>17000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2000</v>
+      </c>
       <c r="X4" t="n">
-        <v>47599000</v>
+        <v>3377000</v>
       </c>
       <c r="Y4" t="n">
-        <v>47599000</v>
+        <v>3377000</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>59785000</v>
+        <v>33170000</v>
       </c>
       <c r="AB4" t="n">
-        <v>12128000</v>
+        <v>1922000</v>
       </c>
       <c r="AC4" t="n">
-        <v>11128000</v>
+        <v>1922000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>31150000</v>
+        <v>17466000</v>
       </c>
       <c r="AF4" t="n">
-        <v>17471000</v>
+        <v>11395000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1934000</v>
       </c>
       <c r="AH4" t="n">
-        <v>13679000</v>
+        <v>4137000</v>
       </c>
       <c r="AI4" t="n">
-        <v>773600000</v>
+        <v>187455000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91845000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>344000</v>
-      </c>
+        <v>114047000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>10000</v>
+      </c>
       <c r="AN4" t="n">
-        <v>45846000</v>
+        <v>26469000</v>
       </c>
       <c r="AO4" t="n">
-        <v>45846000</v>
+        <v>26469000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1240000</v>
+        <v>86028000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1240000</v>
+        <v>86028000</v>
       </c>
       <c r="AR4" t="n">
-        <v>2900000</v>
+        <v>1540000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1879000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1879000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>344000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>39636000</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-161764000</v>
+        <v>-36964000</v>
       </c>
       <c r="AX4" t="n">
-        <v>39636000</v>
+        <v>36964000</v>
       </c>
       <c r="AY4" t="n">
-        <v>677000</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>39636000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>39740000</v>
+        <v>17373000</v>
       </c>
       <c r="BB4" t="n">
-        <v>75466000</v>
+        <v>19591000</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>681755000</v>
+        <v>73408000</v>
       </c>
       <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="n">
-        <v>34614000</v>
-      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
-        <v>63068000</v>
+        <v>13179000</v>
       </c>
       <c r="BH4" t="n">
-        <v>549000</v>
+        <v>478000</v>
       </c>
       <c r="BI4" t="n">
-        <v>-552000</v>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
+        <v>21956000</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1570000</v>
+      </c>
       <c r="BK4" t="n">
-        <v>12185000</v>
+        <v>763000</v>
       </c>
       <c r="BL4" t="n">
-        <v>-1089000</v>
+        <v>-723000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13274000</v>
+        <v>1486000</v>
       </c>
       <c r="BN4" t="n">
-        <v>571891000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>484602000</v>
-      </c>
+        <v>35462000</v>
+      </c>
+      <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="n">
-        <v>87289000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>484602000</v>
-      </c>
+        <v>35462000</v>
+      </c>
+      <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="n">
-        <v>87289000</v>
+        <v>35462000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1077799887</v>
@@ -2231,41 +2235,47 @@
         <v>1077799887</v>
       </c>
       <c r="D5" t="n">
-        <v>57188000</v>
+        <v>9941000</v>
       </c>
       <c r="E5" t="n">
-        <v>277180000</v>
+        <v>73258000</v>
       </c>
       <c r="F5" t="n">
-        <v>279591000</v>
+        <v>75858000</v>
       </c>
       <c r="G5" t="n">
-        <v>633625000</v>
+        <v>19368000</v>
       </c>
       <c r="H5" t="n">
-        <v>277180000</v>
+        <v>73258000</v>
       </c>
       <c r="I5" t="n">
-        <v>57188000</v>
+        <v>7341000</v>
       </c>
       <c r="J5" t="n">
-        <v>279591000</v>
+        <v>73258000</v>
       </c>
       <c r="K5" t="n">
-        <v>279591000</v>
+        <v>73258000</v>
       </c>
       <c r="L5" t="n">
-        <v>687987000</v>
+        <v>66893000</v>
       </c>
       <c r="M5" t="n">
-        <v>408396000</v>
+        <v>-6365000</v>
       </c>
       <c r="N5" t="n">
-        <v>279591000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>73258000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>47452000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1035075000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1023563000</v>
+      </c>
       <c r="R5" t="n">
         <v>335000</v>
       </c>
@@ -2273,147 +2283,137 @@
         <v>335000</v>
       </c>
       <c r="T5" t="n">
-        <v>122038000</v>
+        <v>33586000</v>
       </c>
       <c r="U5" t="n">
-        <v>49731000</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+        <v>5253000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>17000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2000</v>
+      </c>
       <c r="X5" t="n">
-        <v>49731000</v>
+        <v>5234000</v>
       </c>
       <c r="Y5" t="n">
-        <v>49731000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
+        <v>5234000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>72307000</v>
+        <v>28333000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7457000</v>
+        <v>4707000</v>
       </c>
       <c r="AC5" t="n">
-        <v>7457000</v>
+        <v>2107000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2600000</v>
       </c>
       <c r="AE5" t="n">
-        <v>30713000</v>
+        <v>10707000</v>
       </c>
       <c r="AF5" t="n">
-        <v>20472000</v>
+        <v>5047000</v>
       </c>
       <c r="AG5" t="n">
-        <v>188000</v>
+        <v>1347000</v>
       </c>
       <c r="AH5" t="n">
-        <v>10053000</v>
+        <v>4313000</v>
       </c>
       <c r="AI5" t="n">
-        <v>810025000</v>
+        <v>100479000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>104093000</v>
+        <v>52778000</v>
       </c>
       <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>10000</v>
+      </c>
       <c r="AN5" t="n">
-        <v>48615000</v>
+        <v>14215000</v>
       </c>
       <c r="AO5" t="n">
-        <v>48615000</v>
+        <v>14215000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>32701000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>32701000</v>
       </c>
       <c r="AR5" t="n">
-        <v>2900000</v>
+        <v>1310000</v>
       </c>
       <c r="AS5" t="n">
-        <v>2411000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2411000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>50167000</v>
+        <v>4542000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-139107000</v>
+        <v>-35557000</v>
       </c>
       <c r="AX5" t="n">
-        <v>189274000</v>
+        <v>40099000</v>
       </c>
       <c r="AY5" t="n">
-        <v>77000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>78665000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>38775000</v>
+        <v>15964000</v>
       </c>
       <c r="BB5" t="n">
-        <v>71757000</v>
+        <v>24135000</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>705932000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>34897000</v>
-      </c>
+        <v>47701000</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>52642000</v>
+        <v>10319000</v>
       </c>
       <c r="BH5" t="n">
-        <v>565000</v>
+        <v>480000</v>
       </c>
       <c r="BI5" t="n">
-        <v>-5102000</v>
-      </c>
-      <c r="BJ5" t="inlineStr"/>
+        <v>20420000</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1245000</v>
+      </c>
       <c r="BK5" t="n">
-        <v>6283000</v>
+        <v>1597000</v>
       </c>
       <c r="BL5" t="n">
-        <v>-943000</v>
+        <v>-785000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7226000</v>
+        <v>2382000</v>
       </c>
       <c r="BN5" t="n">
-        <v>616647000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>7577000</v>
-      </c>
+        <v>13640000</v>
+      </c>
+      <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="n">
-        <v>609070000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
+        <v>13640000</v>
+      </c>
+      <c r="BQ5" t="inlineStr"/>
       <c r="BR5" t="n">
-        <v>609070000</v>
+        <v>13640000</v>
       </c>
     </row>
   </sheetData>
@@ -2714,616 +2714,616 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-22200000</v>
+        <v>-121371000</v>
       </c>
       <c r="C2" t="n">
-        <v>-9600000</v>
+        <v>-22075000</v>
       </c>
       <c r="D2" t="n">
-        <v>12200000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-9196000</v>
+      </c>
       <c r="F2" t="n">
-        <v>-473000</v>
+        <v>-6213000</v>
       </c>
       <c r="G2" t="n">
-        <v>13640000</v>
+        <v>609070000</v>
       </c>
       <c r="H2" t="n">
-        <v>35462000</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>103122000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-1394000</v>
+      </c>
       <c r="J2" t="n">
-        <v>-21822000</v>
+        <v>507342000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1572000</v>
+        <v>-45961000</v>
       </c>
       <c r="L2" t="n">
-        <v>-395000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>-6441000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-9196000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-9196000</v>
+      </c>
       <c r="O2" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-9600000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>12200000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+        <v>-22075000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>-22075000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-22075000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
       <c r="V2" t="n">
-        <v>1477000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+        <v>668461000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-2275000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
       <c r="Y2" t="n">
-        <v>2264000</v>
+        <v>-540000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2264000</v>
+        <v>8460000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+        <v>-9000000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-2750000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-2750000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>-400000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>680239000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>680239000</v>
+      </c>
       <c r="AF2" t="n">
-        <v>-400000</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-2814000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-2814000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-387000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>86000</v>
-      </c>
+        <v>-3399000</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>-473000</v>
+        <v>-3399000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-21727000</v>
+        <v>-115158000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-17000</v>
+        <v>-1718000</v>
       </c>
       <c r="AN2" t="n">
-        <v>360000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>2057000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
       <c r="AP2" t="n">
-        <v>-828000</v>
+        <v>-18018000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1836000</v>
+        <v>1882000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-5736000</v>
+        <v>9340000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-2000</v>
+        <v>-142000</v>
       </c>
       <c r="AT2" t="n">
-        <v>6746000</v>
+        <v>-29098000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-344000</v>
+        <v>-321102000</v>
       </c>
       <c r="AV2" t="n">
-        <v>157000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>18686000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
       <c r="AX2" t="n">
-        <v>1638000</v>
+        <v>26665000</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1653000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1638000</v>
+        <v>25012000</v>
       </c>
       <c r="BA2" t="n">
-        <v>10220000</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+        <v>13881000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-18426000</v>
+      </c>
       <c r="BC2" t="n">
-        <v>-86000</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>-7608000</v>
       </c>
       <c r="BE2" t="n">
-        <v>-84534000</v>
+        <v>194292000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-16067000</v>
+        <v>-86131000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>1000000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-3525000</v>
+      </c>
       <c r="F3" t="n">
-        <v>-642000</v>
+        <v>-4265000</v>
       </c>
       <c r="G3" t="n">
-        <v>35462000</v>
+        <v>87289000</v>
       </c>
       <c r="H3" t="n">
-        <v>87289000</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>609070000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>51315000</v>
+      </c>
       <c r="J3" t="n">
-        <v>-51827000</v>
+        <v>-573096000</v>
       </c>
       <c r="K3" t="n">
-        <v>-4587000</v>
+        <v>-15065000</v>
       </c>
       <c r="L3" t="n">
-        <v>-385000</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>-4749000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-3525000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-3525000</v>
+      </c>
       <c r="O3" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+        <v>1000000</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1000000</v>
+      </c>
       <c r="V3" t="n">
-        <v>-31815000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+        <v>-476165000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2769000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>23000</v>
+      </c>
       <c r="Y3" t="n">
-        <v>497000</v>
+        <v>-479692000</v>
       </c>
       <c r="Z3" t="n">
-        <v>756000</v>
+        <v>10517000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-259000</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+        <v>-490209000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
       <c r="AD3" t="n">
-        <v>-2454000</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+        <v>-1500000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
       <c r="AF3" t="n">
-        <v>-2454000</v>
+        <v>-1500000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-28000</v>
+        <v>-847000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-28000</v>
+        <v>-847000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-614000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
+        <v>-3418000</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>-614000</v>
+        <v>-3418000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-15425000</v>
+        <v>-81866000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-188000</v>
       </c>
       <c r="AN3" t="n">
-        <v>93000</v>
+        <v>922000</v>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>-2106000</v>
+        <v>-26174000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3158000</v>
+        <v>-15282000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-11242000</v>
+        <v>6860000</v>
       </c>
       <c r="AS3" t="n">
-        <v>71000</v>
+        <v>16000</v>
       </c>
       <c r="AT3" t="n">
-        <v>5907000</v>
+        <v>-17768000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-353000</v>
+        <v>-2363000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1548000</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>11983000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-8583000</v>
+      </c>
       <c r="AX3" t="n">
-        <v>5999000</v>
+        <v>22368000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1160000</v>
+        <v>1392000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4839000</v>
+        <v>20976000</v>
       </c>
       <c r="BA3" t="n">
-        <v>32802000</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
+        <v>1306000</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-1427000</v>
+      </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1393000</v>
       </c>
       <c r="BD3" t="n">
-        <v>42997000</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-60442000</v>
+        <v>-77414000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-86131000</v>
+        <v>-16067000</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-1000000</v>
       </c>
       <c r="D4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-3525000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-4265000</v>
+        <v>-642000</v>
       </c>
       <c r="G4" t="n">
+        <v>35462000</v>
+      </c>
+      <c r="H4" t="n">
         <v>87289000</v>
       </c>
-      <c r="H4" t="n">
-        <v>609070000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>51315000</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>-573096000</v>
+        <v>-51827000</v>
       </c>
       <c r="K4" t="n">
-        <v>-15065000</v>
+        <v>-4587000</v>
       </c>
       <c r="L4" t="n">
-        <v>-4749000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-3525000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-3525000</v>
-      </c>
+        <v>-385000</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1000000</v>
-      </c>
+        <v>-1000000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-476165000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2769000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>23000</v>
-      </c>
+        <v>-31815000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>-479692000</v>
+        <v>497000</v>
       </c>
       <c r="Z4" t="n">
-        <v>10517000</v>
+        <v>756000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-490209000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
+        <v>-259000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-1500000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
+        <v>-2454000</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>-1500000</v>
+        <v>-2454000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-847000</v>
+        <v>-28000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-847000</v>
+        <v>-28000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3418000</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+        <v>-614000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
       <c r="AK4" t="n">
-        <v>-3418000</v>
+        <v>-614000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-81866000</v>
+        <v>-15425000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-188000</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>922000</v>
+        <v>93000</v>
       </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>-26174000</v>
+        <v>-2106000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-15282000</v>
+        <v>3158000</v>
       </c>
       <c r="AR4" t="n">
-        <v>6860000</v>
+        <v>-11242000</v>
       </c>
       <c r="AS4" t="n">
-        <v>16000</v>
+        <v>71000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-17768000</v>
+        <v>5907000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-2363000</v>
+        <v>-353000</v>
       </c>
       <c r="AV4" t="n">
-        <v>11983000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>-8583000</v>
-      </c>
+        <v>1548000</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>22368000</v>
+        <v>5999000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1392000</v>
+        <v>1160000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20976000</v>
+        <v>4839000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1306000</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-1427000</v>
-      </c>
+        <v>32802000</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>1393000</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>42997000</v>
       </c>
       <c r="BE4" t="n">
-        <v>-77414000</v>
+        <v>-60442000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-121371000</v>
+        <v>-22200000</v>
       </c>
       <c r="C5" t="n">
-        <v>-22075000</v>
+        <v>-9600000</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-9196000</v>
-      </c>
+        <v>12200000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-6213000</v>
+        <v>-473000</v>
       </c>
       <c r="G5" t="n">
-        <v>609070000</v>
+        <v>13640000</v>
       </c>
       <c r="H5" t="n">
-        <v>103122000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-1394000</v>
-      </c>
+        <v>35462000</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>507342000</v>
+        <v>-21822000</v>
       </c>
       <c r="K5" t="n">
-        <v>-45961000</v>
+        <v>-1572000</v>
       </c>
       <c r="L5" t="n">
-        <v>-6441000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-9196000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-9196000</v>
-      </c>
+        <v>-395000</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>-22075000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>-22075000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-22075000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
+        <v>2600000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-9600000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>12200000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>668461000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-2275000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
+        <v>1477000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>-540000</v>
+        <v>2264000</v>
       </c>
       <c r="Z5" t="n">
-        <v>8460000</v>
+        <v>2264000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-9000000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-2750000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-2750000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>680239000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>680239000</v>
-      </c>
+        <v>-400000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-400000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-2814000</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2814000</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-3399000</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>-387000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>86000</v>
+      </c>
       <c r="AK5" t="n">
-        <v>-3399000</v>
+        <v>-473000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-115158000</v>
+        <v>-21727000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1718000</v>
+        <v>-17000</v>
       </c>
       <c r="AN5" t="n">
-        <v>2057000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
+        <v>360000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>-18018000</v>
+        <v>-828000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1882000</v>
+        <v>-1836000</v>
       </c>
       <c r="AR5" t="n">
-        <v>9340000</v>
+        <v>-5736000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-142000</v>
+        <v>-2000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-29098000</v>
+        <v>6746000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-321102000</v>
+        <v>-344000</v>
       </c>
       <c r="AV5" t="n">
-        <v>18686000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
+        <v>157000</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>26665000</v>
+        <v>1638000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1653000</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>25012000</v>
+        <v>1638000</v>
       </c>
       <c r="BA5" t="n">
-        <v>13881000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-18426000</v>
-      </c>
+        <v>10220000</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-86000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-7608000</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>194292000</v>
+        <v>-84534000</v>
       </c>
     </row>
   </sheetData>
@@ -3823,132 +3823,132 @@
       </c>
       <c r="CS1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="DS1" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Jingsheng  Lu', 'age': 46, 'title': 'CFO &amp; Executive Chairman', 'yearBorn': 1979, 'fiscalYear': 2024, 'totalPay': 179663, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Runqun  Wang', 'age': 44, 'title': 'Co-Chief Executive Officer', 'yearBorn': 1981, 'fiscalYear': 2024, 'totalPay': 128712, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Jin  Xu', 'age': 41, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1984, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kwok Leung  Ng', 'age': 56, 'title': 'Advisor', 'yearBorn': 1969, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sau Mei  Ng ACIS, ACS, FCIS, FCS', 'age': 48, 'title': 'Company Secretary', 'yearBorn': 1977, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Jingsheng  Lu', 'age': 46, 'title': 'CFO &amp; Executive Chairman', 'yearBorn': 1979, 'fiscalYear': 2024, 'totalPay': 182199, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Runqun  Wang', 'age': 44, 'title': 'Co-Chief Executive Officer', 'yearBorn': 1981, 'fiscalYear': 2024, 'totalPay': 130529, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Jin  Xu', 'age': 41, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1984, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kwok Leung  Ng', 'age': 56, 'title': 'Advisor', 'yearBorn': 1969, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sau Mei  Ng ACIS, ACS, FCIS, FCS', 'age': 48, 'title': 'Company Secretary', 'yearBorn': 1977, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.486</v>
+        <v>1.464</v>
       </c>
       <c r="AD2" t="n">
         <v>200</v>
@@ -4155,7 +4155,7 @@
         <v>16166999</v>
       </c>
       <c r="AL2" t="n">
-        <v>27157513</v>
+        <v>27605232</v>
       </c>
       <c r="AM2" t="n">
         <v>0.015</v>
@@ -4176,7 +4176,7 @@
         <v>0.015</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0196775</v>
+        <v>0.0196075</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
@@ -4214,10 +4214,10 @@
         <v>1077799887</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.00418696</v>
+        <v>0.0042489767</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.5825515</v>
+        <v>3.5302618</v>
       </c>
       <c r="BG2" t="n">
         <v>1735603200</v>
@@ -4244,7 +4244,7 @@
         <v>-0.0625</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -4353,105 +4353,105 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
           <t>OurGame Intl Holdings Ltd.    R</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>Ourgame International Holdings Limited</t>
         </is>
       </c>
-      <c r="CU2" t="n">
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CW2" t="n">
         <v>1772522605</v>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>finmb_266320164</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>Europe/Berlin</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DB2" t="n">
         <v>7200000</v>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>dr_market</t>
         </is>
       </c>
-      <c r="DB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="n">
+      <c r="DD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
         <v>0.015</v>
       </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="n">
+      <c r="DG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="n">
         <v>1613458800000</v>
       </c>
-      <c r="DH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>0.015 - 0.015</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>Frankfurt</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>0</v>
-      </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>0</v>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="inlineStr">
         <is>
           <t>0.015 - 0.05</t>
         </is>
       </c>
-      <c r="DO2" t="n">
+      <c r="DP2" t="n">
         <v>-0.035</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DQ2" t="n">
         <v>-0.7</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="DR2" t="n">
         <v>-6.25</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
       </c>
       <c r="DS2" t="n">
         <v>1731322740</v>
@@ -4472,10 +4472,10 @@
         <v>0</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0.0046774996</v>
+        <v>-0.0046074996</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.23770803</v>
+        <v>-0.2349866</v>
       </c>
       <c r="EA2" t="n">
         <v>15</v>
